--- a/data/trans_bre/IP1020-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1020-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 4,26</t>
+          <t>-0,62; 4,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 2,47</t>
+          <t>-2,89; 2,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 3,76</t>
+          <t>-5,2; 3,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 6,31</t>
+          <t>-2,22; 6,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-86,19; 386,51</t>
+          <t>-98,25; 223,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-60,02; 513,98</t>
+          <t>-62,47; 447,8</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 0,0</t>
+          <t>-2,84; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,75</t>
+          <t>0,73; 6,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 0,0</t>
+          <t>-5,86; -0,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 5,44</t>
+          <t>-2,92; 5,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-80,71; —</t>
+          <t>-84,78; 751,84</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 3,44</t>
+          <t>-2,29; 3,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 5,67</t>
+          <t>-0,67; 5,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 0,0</t>
+          <t>-5,59; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 3,95</t>
+          <t>-5,36; 4,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,29</t>
+          <t>-2,68; 0,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 3,29</t>
+          <t>-0,43; 3,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 2,87</t>
+          <t>-0,21; 3,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 2,65</t>
+          <t>-3,39; 2,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,45; 985,84</t>
+          <t>-64,05; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-68,55; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-72,5; 144,39</t>
+          <t>-68,18; 131,65</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 1,61</t>
+          <t>-2,07; 1,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 3,32</t>
+          <t>-2,08; 3,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 2,35</t>
+          <t>-1,41; 2,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 4,46</t>
+          <t>-2,6; 3,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-74,23; 610,0</t>
+          <t>-70,46; 620,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-69,66; 415,21</t>
+          <t>-70,25; 404,25</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,22</t>
+          <t>0,0; 6,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 10,07</t>
+          <t>-2,37; 10,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 2,03</t>
+          <t>-5,79; 1,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 5,11</t>
+          <t>-7,55; 5,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1236,16</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,77</t>
+          <t>-0,83; 0,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,41</t>
+          <t>0,07; 2,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,56</t>
+          <t>-1,49; 0,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,84</t>
+          <t>-1,46; 1,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-68,11; 176,68</t>
+          <t>-69,27; 201,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,91; 340,91</t>
+          <t>2,29; 319,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-64,0; 48,85</t>
+          <t>-63,28; 61,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-38,34; 77,55</t>
+          <t>-37,84; 81,4</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1020-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1020-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 4,29</t>
+          <t>-0,64; 4,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 2,49</t>
+          <t>-2,86; 2,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 3,35</t>
+          <t>-5,01; 3,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 6,52</t>
+          <t>-2,74; 6,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-98,25; 223,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-62,47; 447,8</t>
+          <t>-59,97; 460,37</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 0,0</t>
+          <t>-2,82; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,91</t>
+          <t>0,73; 6,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,86; -0,59</t>
+          <t>-6,34; -0,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 5,3</t>
+          <t>-2,33; 5,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-84,78; 751,84</t>
+          <t>-81,58; —</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 3,81</t>
+          <t>-2,73; 3,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 5,58</t>
+          <t>-0,72; 5,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 0,0</t>
+          <t>-6,46; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 4,17</t>
+          <t>-6,02; 3,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 0,24</t>
+          <t>-2,42; 0,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 3,59</t>
+          <t>-0,55; 3,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 3,37</t>
+          <t>-0,36; 2,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 2,39</t>
+          <t>-3,13; 2,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,05; —</t>
+          <t>-61,31; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-68,18; 131,65</t>
+          <t>-67,98; 137,92</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 1,6</t>
+          <t>-2,07; 1,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 3,39</t>
+          <t>-2,32; 3,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,37</t>
+          <t>-1,4; 2,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 3,78</t>
+          <t>-2,62; 4,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-70,46; 620,03</t>
+          <t>-72,99; 574,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-70,25; 404,25</t>
+          <t>-71,05; 416,92</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,61</t>
+          <t>0,0; 6,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 10,02</t>
+          <t>-2,47; 9,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 1,27</t>
+          <t>-5,67; 1,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 5,0</t>
+          <t>-7,75; 4,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 972,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,83</t>
+          <t>-0,83; 0,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,46</t>
+          <t>0,06; 2,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,55</t>
+          <t>-1,43; 0,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,97</t>
+          <t>-1,47; 1,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-69,27; 201,0</t>
+          <t>-69,44; 160,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 319,76</t>
+          <t>-3,57; 282,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-63,28; 61,01</t>
+          <t>-63,18; 66,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-37,84; 81,4</t>
+          <t>-38,88; 74,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1020-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1020-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>1,61</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>44,89%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 4,12</t>
+          <t>-0,63; 4,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 2,63</t>
+          <t>-3,04; 2,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 3,45</t>
+          <t>-4,97; 3,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 6,18</t>
+          <t>-3,01; 6,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-86,19; 386,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-59,97; 460,37</t>
+          <t>-60,84; 458,92</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>1,27</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>53,28%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 0,0</t>
+          <t>-2,86; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,77</t>
+          <t>0,72; 5,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,34; -0,59</t>
+          <t>-5,97; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 5,35</t>
+          <t>-2,63; 5,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-81,58; —</t>
+          <t>-81,55; —</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>-0,72</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-23,52%</t>
+          <t>-22,94%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 3,4</t>
+          <t>-2,72; 3,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 5,66</t>
+          <t>-0,73; 5,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 0,0</t>
+          <t>-6,06; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 3,98</t>
+          <t>-5,63; 3,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,43</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-12,93%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 0,26</t>
+          <t>-2,39; 0,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,46</t>
+          <t>-0,61; 3,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,96</t>
+          <t>-0,44; 2,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 2,64</t>
+          <t>-3,08; 3,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-61,31; —</t>
+          <t>-64,45; 985,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-68,55; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-67,98; 137,92</t>
+          <t>-65,95; 201,43</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 1,77</t>
+          <t>-2,07; 1,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 3,4</t>
+          <t>-2,57; 3,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 2,48</t>
+          <t>-1,78; 2,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 4,11</t>
+          <t>-2,81; 4,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-72,99; 574,09</t>
+          <t>-74,23; 610,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-71,05; 416,92</t>
+          <t>-72,64; 415,11</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,76</t>
+          <t>-1,69</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-37,1%</t>
+          <t>-33,65%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,43</t>
+          <t>0,0; 6,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 9,45</t>
+          <t>-2,5; 10,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 1,76</t>
+          <t>-6,4; 2,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 4,22</t>
+          <t>-7,73; 6,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 972,41</t>
+          <t>-100,0; 1236,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,79</t>
+          <t>-0,76; 0,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,36</t>
+          <t>0,18; 2,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 0,65</t>
+          <t>-1,46; 0,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 1,81</t>
+          <t>-1,41; 2,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-69,44; 160,9</t>
+          <t>-68,11; 176,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 282,51</t>
+          <t>5,91; 340,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-63,18; 66,94</t>
+          <t>-64,0; 48,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-38,88; 74,87</t>
+          <t>-34,42; 84,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1020-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1020-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,179 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,74</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,61</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>198,53%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-7,27%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-20,44%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>44,89%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.216728029506501</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.1043424193039755</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.7370285666367503</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.606560139197964</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1.985303204089946</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.07272201980122292</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.2043754024862242</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.4489088760083636</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-0,63; 4,26</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-3,04; 2,47</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-4,97; 3,76</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-3,01; 6,68</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-86,19; 386,51</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-60,84; 458,92</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-0.6267962529565552</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-3.036473352272199</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.965035374431835</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-3.007782531444586</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="n">
+        <v>-0.8619170157068788</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.6084454224246607</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>4.259473813336158</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.467729781250876</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.760339940205592</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>6.679981156381156</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="n">
+        <v>3.865134129526839</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>4.589175024592246</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,36</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,15</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,27</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>53,28%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,86; 0,0</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,72; 5,75</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-5,97; 0,0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-2,63; 5,63</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-81,55; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.5621582452672201</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2.355485692082713</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-2.14747716711852</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.270201368457464</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.5328409466171135</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,65</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,84</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,72</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-15,59%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>227,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-22,94%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.857738999323458</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.7244871401290034</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-5.972745216638543</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-2.62645401704585</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="n">
+        <v>-0.8154593616065289</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,72; 3,44</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-0,73; 5,67</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-6,06; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-5,63; 3,94</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>5.751387992425437</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>5.629484569622021</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +799,177 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,72</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,16</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,23</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-71,05%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>125,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>190,89%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.2132962155079701</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.653395876547745</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.844836162360511</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.7240301659010046</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.1558885302353618</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>2.279031330630371</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.2294211729645547</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,39; 0,29</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-0,61; 3,29</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,44; 2,87</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-3,08; 3,73</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-64,45; 985,84</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-68,55; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-65,95; 201,43</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.722055305018134</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.7250431216649214</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-6.059426325628652</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-5.634633860833018</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>3.443757149681752</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.665023069913413</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.944139923886126</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,33</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,48</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,14</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,36</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-32,03%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>23,17%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>15,21%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>13,83%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,07; 1,61</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,57; 3,32</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,78; 2,35</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-2,81; 4,2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-74,23; 610,0</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-72,64; 415,11</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-0.7176355736430559</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.155486992945804</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.232144457984882</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.1537802301707365</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.7104672066321058</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1.257781111783152</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>1.908939996626765</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.04360398892497103</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>1,86</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2,74</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-1,82</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-1,69</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>104,47%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-63,56%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-33,65%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.389035068736046</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.6095568174376194</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.4406566152654345</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-3.08124593638207</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="n">
+        <v>-0.6445211729111403</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.6854542729375902</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.6594702589561833</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,22</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-2,5; 10,07</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-6,4; 2,03</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-7,73; 6,02</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 1236,16</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.2904247568868717</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.28917263743914</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.869900978372185</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3.72594709863851</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="n">
+        <v>9.858432344365363</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="n">
+        <v>2.014347499947364</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +977,279 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,0</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1,18</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,4</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,34</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,01%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>95,49%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-23,85%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10,24%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-0.3251896905957973</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.4792022895462298</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1409887748120595</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.3592648761708093</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.320330839356357</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.2317472399414955</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.1521362048949838</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.1382846532896911</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-0,76; 0,77</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>0,18; 2,41</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-1,46; 0,56</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-1,41; 2,13</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-68,11; 176,68</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5,91; 340,91</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-64,0; 48,85</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-34,42; 84,69</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.067463535923546</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.567380855761432</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.780021176489054</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.811814699904542</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="n">
+        <v>-0.7422754712297681</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="6" t="n">
+        <v>-0.7263511637072807</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.609720738925955</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.317611383859058</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.347534395922174</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>4.202505496525264</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="n">
+        <v>6.099964808829323</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="6" t="n">
+        <v>4.151124954867495</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1.862229040571759</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2.742429221861643</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-1.815736743905496</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-1.690360764797143</v>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1.044658884882067</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>-0.6356256230297562</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.3364606988354422</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-2.503674463913154</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-6.402199498185299</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-7.733071888683603</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>6.221289152994823</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>10.06663155826898</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>2.028845598799111</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>6.015330632955331</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="n">
+        <v>12.36161451708451</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-7.336225866152318e-05</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>1.182767768158621</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.4044352719791882</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.3382520469546804</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-8.698969594618183e-05</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.9549093073123566</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.2384841789271201</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.1024248687906084</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.7637603225616753</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0.1812871636545108</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-1.459919901291135</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-1.412034314953563</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.6811438128298887</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>0.05908478758828493</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.6400419834639965</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.3442066709246158</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.7700544272836946</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>2.405036217487522</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.5624926513802438</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>2.127527267793506</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>1.766824263431803</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>3.40905205309079</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.4884934088650373</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.8468601391857882</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1257,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
